--- a/cloud_storage/пользователи.xlsx
+++ b/cloud_storage/пользователи.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,60 @@
         <is>
           <t>company_id</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>суперадмин</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>начальник</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>сотрудник</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
